--- a/samples/AUMA-motor-rule.xlsx
+++ b/samples/AUMA-motor-rule.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\web-auma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A66BBC-27C0-44EC-BA5F-C7DA374951E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5919CC1D-8481-4D84-88B5-90A1C85DA114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="580" windowWidth="37140" windowHeight="20160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1070" yWindow="6850" windowWidth="36540" windowHeight="18270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="95">
   <si>
     <t>только 8 цифрт, без других символов.</t>
   </si>
@@ -47,21 +47,12 @@
     <t>Description</t>
   </si>
   <si>
-    <t>{{Article}}</t>
-  </si>
-  <si>
-    <t>Article</t>
-  </si>
-  <si>
     <t>Mains voltage</t>
   </si>
   <si>
     <t>{{Mains voltage}}</t>
   </si>
   <si>
-    <t>Terminal plan TPA</t>
-  </si>
-  <si>
     <t>{{Terminal plan TPA}}</t>
   </si>
   <si>
@@ -99,9 +90,6 @@
   </si>
   <si>
     <t>Set to OPEN (Nm)</t>
-  </si>
-  <si>
-    <t>{{Холостой ток авт. выкл., A}}</t>
   </si>
   <si>
     <t>{{Motor}}</t>
@@ -144,18 +132,12 @@
     <t>после знака "+"два значения.</t>
   </si>
   <si>
-    <t>{{Режим работы1}}</t>
-  </si>
-  <si>
     <t>Insulation class</t>
   </si>
   <si>
     <t>{{Insulation class}}</t>
   </si>
   <si>
-    <t>{{P_N, кВт1}}</t>
-  </si>
-  <si>
     <t>{{(Nm-konc-z)}}</t>
   </si>
   <si>
@@ -186,15 +168,6 @@
     <t>два значения после "V "</t>
   </si>
   <si>
-    <t>{{I_N, A}}</t>
-  </si>
-  <si>
-    <t>{{I_A, A}}</t>
-  </si>
-  <si>
-    <t>{{Высоковольтные испытания [kV]}}</t>
-  </si>
-  <si>
     <t>первые два значения</t>
   </si>
   <si>
@@ -249,66 +222,115 @@
     <t>Правила</t>
   </si>
   <si>
-    <t>"Motor" колонка "Order code" складываем с "Output speed" колонка "Order code" (пример ADXR071-4-0,40-45), данное значение ищем в AUMA-motor.xlsx и из этой строки вставляем значения из столбца "P_N, кВт1"</t>
-  </si>
-  <si>
-    <t>"Motor" колонка "Order code" складываем с "Output speed" колонка "Order code" (пример ADXR071-4-0,40-45), данное значение ищем в AUMA-motor.xlsx и из этой строки вставляем значения из столбца "Режим работы1"</t>
-  </si>
-  <si>
-    <t>"Motor" колонка "Order code" складываем с "Output speed" колонка "Order code" (пример ADXR071-4-0,40-45), данное значение ищем в AUMA-motor.xlsx и из этой строки вставляем значения из столбца "Холостой ток авт. выкл., A"</t>
-  </si>
-  <si>
-    <t>"Motor" колонка "Order code" складываем с "Output speed" колонка "Order code" ((пример ADXR071-4-0,40-45)) , данное значение ищем в AUMA-motor.xlsx и из этой строки вставляем значения из столбца "I_N, A"</t>
-  </si>
-  <si>
-    <t>"Motor" колонка "Order code" складываем с "Output speed" колонка "Order code" (пример ADXR071-4-0,40-45), данное значение ищем в AUMA-motor.xlsx и из этой строки вставляем значения из столбца "I_A, A"</t>
-  </si>
-  <si>
-    <t>"Motor" колонка "Order code" складываем с "Output speed" колонка "Order code" (пример ADXR071-4-0,40-45), данное значение ищем в AUMA-motor.xlsx и из этой строки вставляем значения из столбца "Высоковольтные испытания [kV]"</t>
-  </si>
-  <si>
     <t>первая колонка из .htm</t>
   </si>
   <si>
     <t>{{cos}}</t>
   </si>
   <si>
-    <t>"Motor" колонка "Order code" складываем с "Output speed" колонка "Order code" (пример ADXR071-4-0,40-45), данное значение ищем в AUMA-motor.xlsx и из этой строки вставляем значения из столбца "cos"</t>
-  </si>
-  <si>
-    <t>вместо тире, пробел. (Пример SAEX 10.2)</t>
-  </si>
-  <si>
-    <t>{{nom speed}}</t>
-  </si>
-  <si>
-    <t>"Motor" колонка "Order code" складываем с "Output speed" колонка "Order code" (пример ADXR071-4-0,40-45), данное значение ищем в AUMA-motor.xlsx и из этой строки вставляем значения из столбца "nom speed"</t>
-  </si>
-  <si>
     <t>полное значение, после "RU" вставляется ниже в {{Explosion protection2}} вместе с "RU", если значение умещается в {{Explosion protection}}, тег {{Explosion protection2}} удаляется.</t>
   </si>
   <si>
     <t>первые три значения</t>
+  </si>
+  <si>
+    <t>"Motor" колонка "Order code" складываем с "Output speed" колонка "Order code" (пример ADXR071-4-0,40-45), данное значение ищем в AUMA-motor-2.xlsx и из этой строки вставляем значения из столбца "speed.rpm"</t>
+  </si>
+  <si>
+    <t>"Motor" колонка "Order code" складываем с "Output speed" колонка "Order code" (пример ADXR071-4-0,40-45), данное значение ищем в AUMA-motor-2.xlsx и из этой строки вставляем значения из столбца "cos"</t>
+  </si>
+  <si>
+    <t>{{nom.power.kvt}}</t>
+  </si>
+  <si>
+    <t>"Motor" колонка "Order code" складываем с "Output speed" колонка "Order code" (пример ADXR071-4-0,40-45), данное значение ищем в AUMA-motor-2.xlsx и из этой строки вставляем значения из столбца "nom.power.kvt"</t>
+  </si>
+  <si>
+    <t>{{speed.rpm}}</t>
+  </si>
+  <si>
+    <t>"Motor" колонка "Order code" складываем с "Output speed" колонка "Order code" (пример ADXR071-4-0,40-45), данное значение ищем в AUMA-motor-2.xlsx и из этой строки вставляем значения из столбца "tok.holost.hoda"</t>
+  </si>
+  <si>
+    <t>{{nom.tok.a}}</t>
+  </si>
+  <si>
+    <t>"Motor" колонка "Order code" складываем с "Output speed" колонка "Order code" ((пример ADXR071-4-0,40-45)) , данное значение ищем в AUMA-motor-2.xlsx и из этой строки вставляем значения из столбца "nom.tok.a"</t>
+  </si>
+  <si>
+    <t>{{pysk.tok.a}}</t>
+  </si>
+  <si>
+    <t>"Motor" колонка "Order code" складываем с "Output speed" колонка "Order code" (пример ADXR071-4-0,40-45), данное значение ищем в AUMA-motor-2.xlsx и из этой строки вставляем значения из столбца "pysk.tok.a"</t>
+  </si>
+  <si>
+    <t>{{high.v.test.kvt}}</t>
+  </si>
+  <si>
+    <t>"Motor" колонка "Order code" складываем с "Output speed" колонка "Order code" (пример ADXR071-4-0,40-45), данное значение ищем в AUMA-motor-2.xlsx и из этой строки вставляем значения из столбца "high.v.test.kvt"</t>
+  </si>
+  <si>
+    <t>{{tok.holost.hoda}}</t>
+  </si>
+  <si>
+    <t>Set to CLOSE (Nm) или 	set to</t>
+  </si>
+  <si>
+    <t>Set to OPEN (Nm) или set to</t>
+  </si>
+  <si>
+    <t>{{Type}}</t>
+  </si>
+  <si>
+    <t>вместо тире, пробел. (Пример - SAEX 10.2)</t>
+  </si>
+  <si>
+    <t>значения до "kW" или " kW"</t>
+  </si>
+  <si>
+    <t>{{Motor-kW}}</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Type of duty</t>
+  </si>
+  <si>
+    <t>{{Type of duty}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Temperature version</t>
+  </si>
+  <si>
+    <t>первые семь значений с пробелами, пробелы убрать (пример-S2-15)</t>
+  </si>
+  <si>
+    <t>Terminal plan TPA или Terminal plan</t>
+  </si>
+  <si>
+    <t>Output drive</t>
+  </si>
+  <si>
+    <t>{{Output drive}}</t>
+  </si>
+  <si>
+    <t>{{Electr.connection}}</t>
+  </si>
+  <si>
+    <t>Electr.connection или Ex electrical connection</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -376,18 +398,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -402,26 +418,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -724,440 +736,500 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65304B45-4765-4EC2-9047-ACADC1B45237}">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32.54296875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.26953125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.6328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="47.81640625" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.7265625" style="1"/>
+    <col min="1" max="1" width="51.26953125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="62.26953125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18.6328125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="50" style="3" customWidth="1"/>
+    <col min="5" max="16384" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="2" t="s">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="1" t="s">
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="D35" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="3" t="s">
+      <c r="D36" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="1" t="s">
+      <c r="D37" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>84</v>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/samples/AUMA-motor-rule.xlsx
+++ b/samples/AUMA-motor-rule.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\web-auma\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\web-auma\На сайт-приложение\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5919CC1D-8481-4D84-88B5-90A1C85DA114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0685FCCA-AC4B-4426-AB00-2CC922D6B232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1070" yWindow="6850" windowWidth="36540" windowHeight="18270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2160" yWindow="2160" windowWidth="31710" windowHeight="18270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="97">
   <si>
     <t>только 8 цифрт, без других символов.</t>
   </si>
@@ -228,9 +228,6 @@
     <t>{{cos}}</t>
   </si>
   <si>
-    <t>полное значение, после "RU" вставляется ниже в {{Explosion protection2}} вместе с "RU", если значение умещается в {{Explosion protection}}, тег {{Explosion protection2}} удаляется.</t>
-  </si>
-  <si>
     <t>первые три значения</t>
   </si>
   <si>
@@ -319,6 +316,15 @@
   </si>
   <si>
     <t>Electr.connection или Ex electrical connection</t>
+  </si>
+  <si>
+    <t>{{Explosion protection2}}</t>
+  </si>
+  <si>
+    <t>полное значение до "RU"</t>
+  </si>
+  <si>
+    <t>значения после "RU" вставляется вместе с "RU", если значение умещается в {{Explosion protection}}, тег {{Explosion protection2}} удаляется и ничего не вписывается</t>
   </si>
 </sst>
 </file>
@@ -420,20 +426,20 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -736,7 +742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65304B45-4765-4EC2-9047-ACADC1B45237}">
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="51.26953125" style="3" customWidth="1"/>
@@ -773,16 +779,16 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -804,7 +810,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>2</v>
@@ -857,7 +863,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>20</v>
@@ -866,15 +872,15 @@
         <v>3</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -893,10 +899,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -951,46 +957,44 @@
       <c r="C16" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>64</v>
+      <c r="D16" s="10" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>53</v>
+      <c r="A17" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="10" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>2</v>
@@ -1001,57 +1005,57 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>36</v>
+      <c r="D21" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D22" s="3" t="s">
+      <c r="C23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>39</v>
+      <c r="A24" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>4</v>
@@ -1060,12 +1064,12 @@
         <v>3</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>4</v>
@@ -1074,86 +1078,86 @@
         <v>3</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>88</v>
+        <v>42</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D30" s="3" t="s">
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="4" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="4" t="s">
+      <c r="D33" s="4" t="s">
         <v>76</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>24</v>
@@ -1162,73 +1166,87 @@
         <v>2</v>
       </c>
       <c r="D34" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="7" t="s">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B36" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D36" s="10" t="s">
-        <v>65</v>
+      <c r="D36" s="3" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>86</v>
+        <v>55</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D37" s="4" t="s">
-        <v>89</v>
+      <c r="D37" s="9" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="4" t="s">
+      <c r="B40" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B39" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C39" s="4" t="s">
+      <c r="C40" s="4" t="s">
         <v>2</v>
       </c>
     </row>

--- a/samples/AUMA-motor-rule.xlsx
+++ b/samples/AUMA-motor-rule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\web-auma\На сайт-приложение\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0685FCCA-AC4B-4426-AB00-2CC922D6B232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F158A4D-A7B8-42AE-9BC6-7B6D00075819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2160" yWindow="2160" windowWidth="31710" windowHeight="18270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-2970" yWindow="2030" windowWidth="37790" windowHeight="18270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="97">
   <si>
     <t>только 8 цифрт, без других символов.</t>
   </si>
@@ -231,18 +231,9 @@
     <t>первые три значения</t>
   </si>
   <si>
-    <t>"Motor" колонка "Order code" складываем с "Output speed" колонка "Order code" (пример ADXR071-4-0,40-45), данное значение ищем в AUMA-motor-2.xlsx и из этой строки вставляем значения из столбца "speed.rpm"</t>
-  </si>
-  <si>
-    <t>"Motor" колонка "Order code" складываем с "Output speed" колонка "Order code" (пример ADXR071-4-0,40-45), данное значение ищем в AUMA-motor-2.xlsx и из этой строки вставляем значения из столбца "cos"</t>
-  </si>
-  <si>
     <t>{{nom.power.kvt}}</t>
   </si>
   <si>
-    <t>"Motor" колонка "Order code" складываем с "Output speed" колонка "Order code" (пример ADXR071-4-0,40-45), данное значение ищем в AUMA-motor-2.xlsx и из этой строки вставляем значения из столбца "nom.power.kvt"</t>
-  </si>
-  <si>
     <t>{{speed.rpm}}</t>
   </si>
   <si>
@@ -252,21 +243,12 @@
     <t>{{nom.tok.a}}</t>
   </si>
   <si>
-    <t>"Motor" колонка "Order code" складываем с "Output speed" колонка "Order code" ((пример ADXR071-4-0,40-45)) , данное значение ищем в AUMA-motor-2.xlsx и из этой строки вставляем значения из столбца "nom.tok.a"</t>
-  </si>
-  <si>
     <t>{{pysk.tok.a}}</t>
   </si>
   <si>
-    <t>"Motor" колонка "Order code" складываем с "Output speed" колонка "Order code" (пример ADXR071-4-0,40-45), данное значение ищем в AUMA-motor-2.xlsx и из этой строки вставляем значения из столбца "pysk.tok.a"</t>
-  </si>
-  <si>
     <t>{{high.v.test.kvt}}</t>
   </si>
   <si>
-    <t>"Motor" колонка "Order code" складываем с "Output speed" колонка "Order code" (пример ADXR071-4-0,40-45), данное значение ищем в AUMA-motor-2.xlsx и из этой строки вставляем значения из столбца "high.v.test.kvt"</t>
-  </si>
-  <si>
     <t>{{tok.holost.hoda}}</t>
   </si>
   <si>
@@ -325,18 +307,52 @@
   </si>
   <si>
     <t>значения после "RU" вставляется вместе с "RU", если значение умещается в {{Explosion protection}}, тег {{Explosion protection2}} удаляется и ничего не вписывается</t>
+  </si>
+  <si>
+    <t>"Motor" колонка "Order code" складываем с "Output speed" колонка "Order code" (пример ADXR071-4-0,40-45), данное значение ищем в AUMA-motor-2.xlsx в колонке "moto.speed" и из этой строки вставляем значения из столбца "nom.power.kvt"</t>
+  </si>
+  <si>
+    <t>"Motor" колонка "Order code" складываем с "Output speed" колонка "Order code" (пример ADXR071-4-0,40-45), данное значение ищем в AUMA-motor-2.xlsx в колонке "moto.speed" и из этой строки вставляем значения из столбца "speed.rpm"</t>
+  </si>
+  <si>
+    <t>"Motor" колонка "Order code" складываем с "Output speed" колонка "Order code" (пример ADXR071-4-0,40-45) , данное значение ищем в AUMA-motor-2.xlsx в колонке "moto.speed" и из этой строки вставляем значения из столбца "nom.tok.a"</t>
+  </si>
+  <si>
+    <t>"Motor" колонка "Order code" складываем с "Output speed" колонка "Order code" (пример ADXR071-4-0,40-45), данное значение ищем в AUMA-motor-2.xlsx в колонке "moto.speed" и из этой строки вставляем значения из столбца "pysk.tok.a"</t>
+  </si>
+  <si>
+    <t>"Motor" колонка "Order code" складываем с "Output speed" колонка "Order code" (пример ADXR071-4-0,40-45), данное значение ищем в AUMA-motor-2.xlsx в колонке "moto.speed" и из этой строки вставляем значения из столбца "cos"</t>
+  </si>
+  <si>
+    <t>"Motor" колонка "Order code" складываем с "Output speed" колонка "Order code" (пример ADXR071-4-0,40-45), данное значение ищем в AUMA-motor-2.xlsx в колонке "moto.speed" и из этой строки вставляем значения из столбца "high.v.test.kvt"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -424,21 +440,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -779,16 +797,16 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -810,7 +828,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>2</v>
@@ -863,7 +881,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>20</v>
@@ -872,15 +890,15 @@
         <v>3</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -899,10 +917,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -958,19 +976,19 @@
         <v>3</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="10" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -994,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>2</v>
@@ -1008,7 +1026,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>2</v>
@@ -1047,10 +1065,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -1100,7 +1118,7 @@
         <v>56</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>3</v>
@@ -1114,7 +1132,7 @@
         <v>57</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>3</v>
@@ -1125,34 +1143,34 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D32" s="8" t="s">
-        <v>66</v>
+      <c r="D32" s="12" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
@@ -1213,24 +1231,24 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>2</v>
@@ -1240,14 +1258,17 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="4" t="s">
-        <v>92</v>
+      <c r="A40" s="11" t="s">
+        <v>86</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>2</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
